--- a/04_Network/03_preserve_modules/c_data/03_preserve_modules.xlsx
+++ b/04_Network/03_preserve_modules/c_data/03_preserve_modules.xlsx
@@ -5857,7 +5857,7 @@
     <t>04_Network/01_build_modules/c_data/modules.rds</t>
   </si>
   <si>
-    <t>8575e2b797d792ac287f40ef0a0fba35</t>
+    <t>d9a37515570be8efb6716b246dda0527</t>
   </si>
   <si>
     <t>package</t>
